--- a/reports/packet_features.xlsx
+++ b/reports/packet_features.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/blainewever/Desktop/ML/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bweve\OneDrive\Desktop\School\ml-iot-detection\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{869E77D2-AB48-BD41-8FCA-D9A21EE02FC9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF9B6C5-B3C7-4175-9F42-43EA8481C766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="660" windowWidth="30240" windowHeight="18980" xr2:uid="{68EE72A8-8B36-ED4F-97F1-A019F73611DA}"/>
+    <workbookView xWindow="14100" yWindow="0" windowWidth="24405" windowHeight="20985" xr2:uid="{68EE72A8-8B36-ED4F-97F1-A019F73611DA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="89">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
   <si>
     <t>L4_tcp</t>
   </si>
@@ -122,9 +122,6 @@
     <t>The total size of the Layer 2 Ethernet frame.</t>
   </si>
   <si>
-    <t>epoch_timestamp</t>
-  </si>
-  <si>
     <t>The absolute UNIX timestamp when the packet was captured.</t>
   </si>
   <si>
@@ -191,39 +188,6 @@
     <t>The mode (most frequent) destination port in the window.</t>
   </si>
   <si>
-    <t>The total sum of the values in the window.</t>
-  </si>
-  <si>
-    <t>The minimum value observed in the window.</t>
-  </si>
-  <si>
-    <t>The maximum value observed in the window.</t>
-  </si>
-  <si>
-    <t>The median (50th percentile) value in the window.</t>
-  </si>
-  <si>
-    <t>The mean value of the window.</t>
-  </si>
-  <si>
-    <t>The variance, indicating how spread out the values are from the average.</t>
-  </si>
-  <si>
-    <t>Skewness; a measure of the asymmetry of the probability distribution (e.g., mostly small packets with a few large ones).</t>
-  </si>
-  <si>
-    <t>Kurtosis; a measure of the "tailedness" of the distribution (identifying outliers or heavy tails).</t>
-  </si>
-  <si>
-    <t>The first quartile (25th percentile).</t>
-  </si>
-  <si>
-    <t>The third quartile (75th percentile).</t>
-  </si>
-  <si>
-    <t>The Interquartile Range (Q3 - Q1), measuring the statistical dispersion of the middle 50% of the data.</t>
-  </si>
-  <si>
     <t>global_category</t>
   </si>
   <si>
@@ -251,43 +215,154 @@
     <t>The destination IP address. (The _new suffix often indicates it has been mapped, encoded, or anonymized for model ingestion).</t>
   </si>
   <si>
-    <t>sum_et, sum_e</t>
-  </si>
-  <si>
-    <t>min_et, min_e</t>
-  </si>
-  <si>
-    <t>max_et, max_e</t>
-  </si>
-  <si>
-    <t>med_et, med</t>
-  </si>
-  <si>
-    <t>average_et, average</t>
-  </si>
-  <si>
-    <t>var, var_e</t>
-  </si>
-  <si>
-    <t>skew_et, skew_e</t>
-  </si>
-  <si>
-    <t>kurt_et, kurt_e</t>
-  </si>
-  <si>
-    <t>q1, q1_e</t>
-  </si>
-  <si>
-    <t>q3, q3_e</t>
-  </si>
-  <si>
-    <t>iqr, iqr_e</t>
-  </si>
-  <si>
     <t>Feature</t>
   </si>
   <si>
-    <t>Classification</t>
+    <t>Keep</t>
+  </si>
+  <si>
+    <t>Maybe</t>
+  </si>
+  <si>
+    <t>Discard</t>
+  </si>
+  <si>
+    <t>Classification Features</t>
+  </si>
+  <si>
+    <t>sum_et</t>
+  </si>
+  <si>
+    <t>min_et</t>
+  </si>
+  <si>
+    <t>max_et</t>
+  </si>
+  <si>
+    <t>average_et</t>
+  </si>
+  <si>
+    <t>med_et</t>
+  </si>
+  <si>
+    <t>skew_et</t>
+  </si>
+  <si>
+    <t>kurt_et</t>
+  </si>
+  <si>
+    <t>var</t>
+  </si>
+  <si>
+    <t>q3</t>
+  </si>
+  <si>
+    <t>q1</t>
+  </si>
+  <si>
+    <t>iqr</t>
+  </si>
+  <si>
+    <t>sum_e</t>
+  </si>
+  <si>
+    <t>med</t>
+  </si>
+  <si>
+    <t>max_e</t>
+  </si>
+  <si>
+    <t>skew_e</t>
+  </si>
+  <si>
+    <t>q3_e</t>
+  </si>
+  <si>
+    <t>q1_e</t>
+  </si>
+  <si>
+    <t>iqr_e</t>
+  </si>
+  <si>
+    <t>epoch_timesetamp</t>
+  </si>
+  <si>
+    <t>The total accumulated elapsed time (inter-arrival time) between all packets within the current aggregation window.</t>
+  </si>
+  <si>
+    <t>The smallest recorded elapsed time between any two consecutive packets in the window.</t>
+  </si>
+  <si>
+    <t>The largest recorded elapsed time between any two consecutive packets in the window.</t>
+  </si>
+  <si>
+    <t>The median (50th percentile) elapsed time between packets in the window.</t>
+  </si>
+  <si>
+    <t>The arithmetic mean of the elapsed times between packets in the window.</t>
+  </si>
+  <si>
+    <t>The skewness of the elapsed time distribution, measuring its asymmetry (e.g., mostly short intervals with a few long delays).</t>
+  </si>
+  <si>
+    <t>The kurtosis of the elapsed time distribution, measuring the "tailedness" to help identify extreme timing anomalies or outliers.</t>
+  </si>
+  <si>
+    <t>The variance of the elapsed times, indicating how spread out the inter-arrival times are from the average.</t>
+  </si>
+  <si>
+    <t>The third quartile (75th percentile) value of the elapsed times in the window.</t>
+  </si>
+  <si>
+    <t>The first quartile (25th percentile) value of the elapsed times in the window.</t>
+  </si>
+  <si>
+    <t>The interquartile range (Q3 - Q1) for elapsed times, measuring the statistical dispersion of the middle 50% of the timing data.</t>
+  </si>
+  <si>
+    <t>The total sum of all Ethernet frame sizes (in bytes) captured within the window.</t>
+  </si>
+  <si>
+    <t>min_e</t>
+  </si>
+  <si>
+    <t>The smallest Ethernet frame size observed in the window.</t>
+  </si>
+  <si>
+    <t>The largest Ethernet frame size observed in the window.</t>
+  </si>
+  <si>
+    <t>The median (50th percentile) Ethernet frame size in the window.</t>
+  </si>
+  <si>
+    <t>average</t>
+  </si>
+  <si>
+    <t>The arithmetic mean of the Ethernet frame sizes in the window.</t>
+  </si>
+  <si>
+    <t>The skewness of the Ethernet frame size distribution, measuring its asymmetry.</t>
+  </si>
+  <si>
+    <t>kurt_e</t>
+  </si>
+  <si>
+    <t>The kurtosis of the Ethernet frame size distribution, identifying how prone the window is to extreme outlier packet sizes.</t>
+  </si>
+  <si>
+    <t>var_e</t>
+  </si>
+  <si>
+    <t>The variance of the Ethernet frame sizes, indicating the spread of packet sizes from the average.</t>
+  </si>
+  <si>
+    <t>The third quartile (75th percentile) value of the Ethernet frame sizes in the window.</t>
+  </si>
+  <si>
+    <t>The first quartile (25th percentile) value of the Ethernet frame sizes in the window.</t>
+  </si>
+  <si>
+    <t>The interquartile range (Q3 - Q1) for Ethernet frame sizes, capturing the spread of the middle 50% of the packet size data.</t>
   </si>
   <si>
     <r>
@@ -297,38 +372,26 @@
       <rPr>
         <i/>
         <sz val="14"/>
-        <color theme="1"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
       </rPr>
       <t>unique</t>
     </r>
     <r>
       <rPr>
         <sz val="14"/>
-        <color theme="1"/>
         <rFont val="Aptos Narrow"/>
+        <family val="2"/>
       </rPr>
       <t xml:space="preserve"> Layer 3 destination IP addresses communicated with during the window.</t>
     </r>
-  </si>
-  <si>
-    <t>Keep</t>
-  </si>
-  <si>
-    <t>Maybe</t>
-  </si>
-  <si>
-    <t>Discard</t>
-  </si>
-  <si>
-    <t>a</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -342,12 +405,6 @@
       <name val="Aptos Narrow"/>
     </font>
     <font>
-      <i/>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
       <b/>
       <sz val="14"/>
       <color theme="1"/>
@@ -356,13 +413,39 @@
     <font>
       <sz val="14"/>
       <color theme="1"/>
-      <name val="Marlett"/>
-      <charset val="2"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="14"/>
-      <color rgb="FF000000"/>
+      <color theme="1"/>
       <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF1F1F1F"/>
+      <name val="Arial"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="14"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="4">
@@ -385,7 +468,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -393,38 +476,48 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <extLst>
+        <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
+          <xfpb:xfComplement i="0"/>
+        </ext>
+      </extLst>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -440,6 +533,23 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/featurePropertyBag/featurePropertyBag.xml><?xml version="1.0" encoding="utf-8"?>
+<FeaturePropertyBags xmlns="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag">
+  <bag type="Checkbox"/>
+  <bag type="XFControls">
+    <bagId k="CellControl">0</bagId>
+  </bag>
+  <bag type="XFComplement">
+    <bagId k="XFControls">1</bagId>
+  </bag>
+  <bag type="XFComplements" extRef="XFComplementsMapperExtRef">
+    <a k="MappedFeaturePropertyBags">
+      <bagId>2</bagId>
+    </a>
+  </bag>
+</FeaturePropertyBags>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -760,492 +870,899 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C6F6C96-AC79-6243-AE19-8A543CB4672D}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:E50"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="19" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:E68"/>
+  <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="38.83203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="121.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="39.75" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="124.75" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="5" width="10" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="10.83203125" style="1"/>
+    <col min="6" max="16384" width="10.875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
-        <v>82</v>
+        <v>59</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="6" t="s">
+      <c r="C1" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="12" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="12" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="12" t="s">
+        <v>10</v>
+      </c>
+      <c r="C3" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="12" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="C5" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="12" t="s">
+        <v>8</v>
+      </c>
+      <c r="B6" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="B7" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="C7" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D7" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="12" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="12" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C9" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B10" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C10" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D10" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="12" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="C11" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D11" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="B12" s="12" t="s">
+        <v>25</v>
+      </c>
+      <c r="C12" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="12" t="s">
+        <v>5</v>
+      </c>
+      <c r="B13" s="12" t="s">
+        <v>16</v>
+      </c>
+      <c r="C13" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="B14" s="12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C14" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="12" t="s">
+        <v>7</v>
+      </c>
+      <c r="B15" s="12" t="s">
+        <v>14</v>
+      </c>
+      <c r="C15" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="12" t="s">
+        <v>33</v>
+      </c>
+      <c r="B16" s="12" t="s">
+        <v>34</v>
+      </c>
+      <c r="C16" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="12" t="s">
+        <v>35</v>
+      </c>
+      <c r="B17" s="12" t="s">
+        <v>36</v>
+      </c>
+      <c r="C17" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D17" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="12" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="12" t="s">
+        <v>38</v>
+      </c>
+      <c r="C18" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D18" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="12" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="C19" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D19" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="B20" s="12" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D20" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="12" t="s">
+        <v>42</v>
+      </c>
+      <c r="B21" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="C21" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>45</v>
+      </c>
+      <c r="C22" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D22" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="B23" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="C23" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="B24" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="C24" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="13" t="s">
+        <v>64</v>
+      </c>
+      <c r="B25" s="13" t="s">
+        <v>83</v>
+      </c>
+      <c r="C25" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D25" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="13" t="s">
+        <v>65</v>
+      </c>
+      <c r="B26" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="C26" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D26" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="13" t="s">
+        <v>66</v>
+      </c>
+      <c r="B27" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="C27" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D27" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="13" t="s">
+        <v>68</v>
+      </c>
+      <c r="B28" s="13" t="s">
         <v>86</v>
       </c>
-      <c r="E1" s="6" t="s">
+      <c r="C28" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D28" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="13" t="s">
+        <v>67</v>
+      </c>
+      <c r="B29" s="13" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="5" t="s">
+      <c r="C29" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D29" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E29" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="13" t="s">
+        <v>69</v>
+      </c>
+      <c r="B30" s="13" t="s">
         <v>88</v>
       </c>
-      <c r="D2" s="5"/>
-      <c r="E2" s="5"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="1" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D5" s="5"/>
-      <c r="E5" s="5"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D6" s="5"/>
-      <c r="E6" s="5"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C7" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D7" s="5"/>
-      <c r="E7" s="5"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="C8" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C9" s="5"/>
-      <c r="D9" s="5" t="s">
-        <v>88</v>
-      </c>
-      <c r="E9" s="5"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>9</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>12</v>
-      </c>
-      <c r="C10" s="5"/>
-      <c r="D10" s="5"/>
-      <c r="E10" s="5"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B11" s="1" t="s">
+      <c r="C30" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D30" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E30" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="13" t="s">
         <v>70</v>
       </c>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C12" s="5"/>
-      <c r="D12" s="5"/>
-      <c r="E12" s="5"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="B13" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C13" s="5"/>
-      <c r="D13" s="5"/>
-      <c r="E13" s="5"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C14" s="5"/>
-      <c r="D14" s="5"/>
-      <c r="E14" s="5"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C15" s="5"/>
-      <c r="D15" s="5"/>
-      <c r="E15" s="5"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="B31" s="13" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D31" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E31" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="13" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" s="13" t="s">
+        <v>90</v>
+      </c>
+      <c r="C32" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D32" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E32" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="13" t="s">
+        <v>72</v>
+      </c>
+      <c r="B33" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="C33" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D33" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E33" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="13" t="s">
+        <v>73</v>
+      </c>
+      <c r="B34" s="13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C34" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D34" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E34" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="13" t="s">
+        <v>74</v>
+      </c>
+      <c r="B35" s="13" t="s">
+        <v>93</v>
+      </c>
+      <c r="C35" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D35" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E35" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="13" t="s">
+        <v>75</v>
+      </c>
+      <c r="B36" s="13" t="s">
+        <v>94</v>
+      </c>
+      <c r="C36" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D36" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E36" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="13" t="s">
+        <v>95</v>
+      </c>
+      <c r="B37" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="C37" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D37" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E37" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="13" t="s">
+        <v>77</v>
+      </c>
+      <c r="B38" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="C38" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D38" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E38" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="13" t="s">
+        <v>76</v>
+      </c>
+      <c r="B39" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="C39" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D39" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E39" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="B40" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="C40" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D40" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E40" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="13" t="s">
+        <v>78</v>
+      </c>
+      <c r="B41" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="C41" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D41" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E41" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="B42" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="C42" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D42" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E42" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="B43" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="C43" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D43" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E43" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="B44" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="C44" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D44" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E44" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="B45" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C45" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D45" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E45" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="B46" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="C46" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D46" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E46" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="B47" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B16" s="1" t="s">
+      <c r="C47" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D47" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E47" s="8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+      <c r="B48" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="C48" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D48" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E48" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="1" t="s">
+      <c r="B49" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="B18" s="1" t="s">
-        <v>33</v>
-      </c>
-      <c r="C18" s="5"/>
-      <c r="D18" s="5"/>
-      <c r="E18" s="5"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="5"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="1" t="s">
-        <v>36</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>37</v>
-      </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="5"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="5"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>41</v>
-      </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="5"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="5"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="5"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B25" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="B26" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
-      <c r="E26" s="5"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="B27" s="1" t="s">
+      <c r="C49" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D49" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E49" s="8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A50" s="7"/>
+    </row>
+    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A51" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B51" s="3"/>
+    </row>
+    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A52" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
-      <c r="E27" s="5"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B28" s="1" t="s">
+      <c r="B52" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
-      <c r="E28" s="5"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="1" t="s">
-        <v>72</v>
-      </c>
-      <c r="B29" s="1" t="s">
+    </row>
+    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A53" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
-      <c r="E29" s="5"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="B30" s="1" t="s">
+      <c r="B53" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
-      <c r="E30" s="5"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="1" t="s">
-        <v>74</v>
-      </c>
-      <c r="B31" s="1" t="s">
+    </row>
+    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A54" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
-      <c r="E31" s="5"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="B32" s="1" t="s">
+      <c r="B54" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="C32" s="5"/>
-      <c r="D32" s="5"/>
-      <c r="E32" s="5"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="B33" s="1" t="s">
+    </row>
+    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A55" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C33" s="5"/>
-      <c r="D33" s="5"/>
-      <c r="E33" s="5"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="B34" s="1" t="s">
+      <c r="B55" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="C34" s="5"/>
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B35" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C35" s="5"/>
-      <c r="D35" s="5"/>
-      <c r="E35" s="5"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="C36" s="5"/>
-      <c r="D36" s="5"/>
-      <c r="E36" s="5"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B38" s="1" t="s">
-        <v>61</v>
-      </c>
-      <c r="C38" s="5"/>
-      <c r="D38" s="5"/>
-      <c r="E38" s="5"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="B46" s="3"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="B48" s="1" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A49" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="B49" s="1" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A50" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>69</v>
-      </c>
+    </row>
+    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A59" s="9"/>
+      <c r="B59" s="9"/>
+    </row>
+    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A60" s="10"/>
+      <c r="B60" s="11"/>
+    </row>
+    <row r="68" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C68" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/reports/packet_features.xlsx
+++ b/reports/packet_features.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bweve\OneDrive\Desktop\School\ml-iot-detection\reports\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF9B6C5-B3C7-4175-9F42-43EA8481C766}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DBF5288-191A-458F-91F9-5F15409406CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14100" yWindow="0" windowWidth="24405" windowHeight="20985" xr2:uid="{68EE72A8-8B36-ED4F-97F1-A019F73611DA}"/>
+    <workbookView xWindow="5085" yWindow="5535" windowWidth="28800" windowHeight="15345" xr2:uid="{68EE72A8-8B36-ED4F-97F1-A019F73611DA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,9 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="110">
   <si>
-    <t>L4_tcp</t>
-  </si>
-  <si>
     <t>Binary flag (1/0) indicating the use of the Transmission Control Protocol (TCP).</t>
   </si>
   <si>
@@ -385,6 +382,9 @@
       </rPr>
       <t xml:space="preserve"> Layer 3 destination IP addresses communicated with during the window.</t>
     </r>
+  </si>
+  <si>
+    <t>L4_tcp</t>
   </si>
 </sst>
 </file>
@@ -480,7 +480,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -489,7 +489,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
       <extLst>
         <ext xmlns:xfpb="http://schemas.microsoft.com/office/spreadsheetml/2022/featurepropertybag" uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -505,17 +505,16 @@
         </ext>
       </extLst>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -870,7 +869,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6C6F6C96-AC79-6243-AE19-8A543CB4672D}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:E68"/>
+  <dimension ref="A1:E60"/>
   <sheetFormatPr defaultColWidth="10.875" defaultRowHeight="18.75" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="39.75" style="1" bestFit="1" customWidth="1"/>
@@ -881,826 +880,826 @@
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="D1" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>0</v>
+      </c>
+      <c r="C2" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D2" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E2" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E3" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D4" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E4" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="11" t="s">
+        <v>3</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D5" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E5" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="11" t="s">
+        <v>7</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>12</v>
+      </c>
+      <c r="C6" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D6" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E6" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="11" t="s">
+        <v>8</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>11</v>
+      </c>
+      <c r="C7" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D7" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D8" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E8" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="11" t="s">
         <v>18</v>
       </c>
-      <c r="C1" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="12" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>1</v>
-      </c>
-      <c r="C2" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D2" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E2" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="12" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D3" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E3" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D4" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E4" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="12" t="s">
+      <c r="B9" s="11" t="s">
+        <v>57</v>
+      </c>
+      <c r="C9" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D9" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E9" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="11" t="s">
+        <v>25</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D10" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E10" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C11" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D11" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="11" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D12" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E12" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="11" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="12" t="s">
-        <v>17</v>
-      </c>
-      <c r="C5" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D5" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E5" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A6" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" s="12" t="s">
+      <c r="B13" s="11" t="s">
+        <v>15</v>
+      </c>
+      <c r="C13" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D13" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C14" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D14" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E14" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="B15" s="11" t="s">
         <v>13</v>
       </c>
-      <c r="C6" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D6" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E6" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A7" s="12" t="s">
-        <v>9</v>
-      </c>
-      <c r="B7" s="12" t="s">
-        <v>12</v>
-      </c>
-      <c r="C7" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D7" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E7" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A8" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D8" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E8" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A9" s="12" t="s">
-        <v>19</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="C9" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="D9" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E9" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A10" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B10" s="12" t="s">
+      <c r="C15" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D15" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E15" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="11" t="s">
+        <v>32</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="C16" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D16" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E16" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A17" s="11" t="s">
+        <v>34</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>35</v>
+      </c>
+      <c r="C17" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D17" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E17" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A18" s="11" t="s">
+        <v>36</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>37</v>
+      </c>
+      <c r="C18" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D18" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E18" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A19" s="11" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D19" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E19" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A20" s="11" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>108</v>
+      </c>
+      <c r="C20" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D20" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E20" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A21" s="11" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" s="6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" s="11" t="s">
+        <v>43</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>44</v>
+      </c>
+      <c r="C22" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D22" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E22" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" s="11" t="s">
+        <v>45</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>46</v>
+      </c>
+      <c r="C23" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D23" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E23" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" s="11" t="s">
+        <v>47</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C24" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="D24" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E24" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D25" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E25" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" s="12" t="s">
+        <v>64</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="C26" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D26" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A27" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="B27" s="12" t="s">
+        <v>84</v>
+      </c>
+      <c r="C27" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D27" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A28" s="12" t="s">
+        <v>67</v>
+      </c>
+      <c r="B28" s="12" t="s">
+        <v>85</v>
+      </c>
+      <c r="C28" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D28" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E28" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A29" s="12" t="s">
+        <v>66</v>
+      </c>
+      <c r="B29" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C29" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D29" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E29" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A30" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="B30" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C30" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D30" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E30" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A31" s="12" t="s">
+        <v>69</v>
+      </c>
+      <c r="B31" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="C31" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D31" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E31" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A32" s="12" t="s">
+        <v>70</v>
+      </c>
+      <c r="B32" s="12" t="s">
+        <v>89</v>
+      </c>
+      <c r="C32" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D32" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E32" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A33" s="12" t="s">
+        <v>71</v>
+      </c>
+      <c r="B33" s="12" t="s">
+        <v>90</v>
+      </c>
+      <c r="C33" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D33" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E33" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A34" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="B34" s="12" t="s">
+        <v>91</v>
+      </c>
+      <c r="C34" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D34" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E34" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A35" s="12" t="s">
+        <v>73</v>
+      </c>
+      <c r="B35" s="12" t="s">
+        <v>92</v>
+      </c>
+      <c r="C35" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D35" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E35" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A36" s="12" t="s">
+        <v>74</v>
+      </c>
+      <c r="B36" s="12" t="s">
+        <v>93</v>
+      </c>
+      <c r="C36" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D36" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E36" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A37" s="12" t="s">
+        <v>94</v>
+      </c>
+      <c r="B37" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="C37" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D37" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E37" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A38" s="12" t="s">
+        <v>76</v>
+      </c>
+      <c r="B38" s="12" t="s">
+        <v>96</v>
+      </c>
+      <c r="C38" s="6" t="b">
+        <v>1</v>
+      </c>
+      <c r="D38" s="6" t="b">
+        <v>0</v>
+      </c>
+      <c r="E38" s="6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A39" s="12" t="s">
+        <v>75</v>
+      </c>
+      <c r="B39" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="C39" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D39" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E39" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A40" s="12" t="s">
+        <v>98</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="C40" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D40" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E40" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A41" s="12" t="s">
+        <v>77</v>
+      </c>
+      <c r="B41" s="12" t="s">
+        <v>100</v>
+      </c>
+      <c r="C41" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D41" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E41" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A42" s="12" t="s">
+        <v>101</v>
+      </c>
+      <c r="B42" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="C42" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D42" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E42" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A43" s="12" t="s">
+        <v>103</v>
+      </c>
+      <c r="B43" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="C43" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D43" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E43" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A44" s="12" t="s">
+        <v>78</v>
+      </c>
+      <c r="B44" s="12" t="s">
+        <v>105</v>
+      </c>
+      <c r="C44" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D44" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E44" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A45" s="12" t="s">
+        <v>79</v>
+      </c>
+      <c r="B45" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="C45" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D45" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E45" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A46" s="12" t="s">
+        <v>80</v>
+      </c>
+      <c r="B46" s="12" t="s">
+        <v>107</v>
+      </c>
+      <c r="C46" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D46" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E46" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A47" s="11" t="s">
+        <v>81</v>
+      </c>
+      <c r="B47" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="C10" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D10" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E10" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A11" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="B11" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="C11" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D11" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E11" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A12" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B12" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="C12" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D12" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E12" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A13" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>16</v>
-      </c>
-      <c r="C13" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D13" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E13" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A14" s="12" t="s">
-        <v>6</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>15</v>
-      </c>
-      <c r="C14" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="D14" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E14" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A15" s="12" t="s">
-        <v>7</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="D15" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E15" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A16" s="12" t="s">
-        <v>33</v>
-      </c>
-      <c r="B16" s="12" t="s">
-        <v>34</v>
-      </c>
-      <c r="C16" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="D16" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E16" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A17" s="12" t="s">
-        <v>35</v>
-      </c>
-      <c r="B17" s="12" t="s">
-        <v>36</v>
-      </c>
-      <c r="C17" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D17" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E17" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A18" s="12" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D18" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E18" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A19" s="12" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>40</v>
-      </c>
-      <c r="C19" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D19" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E19" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A20" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="B20" s="12" t="s">
-        <v>109</v>
-      </c>
-      <c r="C20" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D20" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E20" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A21" s="12" t="s">
-        <v>42</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="D21" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E21" s="6" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A22" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D22" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E22" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A23" s="12" t="s">
-        <v>46</v>
-      </c>
-      <c r="B23" s="12" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="D23" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E23" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A24" s="12" t="s">
-        <v>48</v>
-      </c>
-      <c r="B24" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="C24" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="D24" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="E24" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A25" s="13" t="s">
-        <v>64</v>
-      </c>
-      <c r="B25" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C25" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D25" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E25" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="13" t="s">
-        <v>65</v>
-      </c>
-      <c r="B26" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C26" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D26" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E26" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="13" t="s">
-        <v>66</v>
-      </c>
-      <c r="B27" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C27" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D27" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E27" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A28" s="13" t="s">
-        <v>68</v>
-      </c>
-      <c r="B28" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C28" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D28" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E28" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A29" s="13" t="s">
-        <v>67</v>
-      </c>
-      <c r="B29" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="C29" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D29" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E29" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A30" s="13" t="s">
-        <v>69</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="C30" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D30" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E30" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A31" s="13" t="s">
-        <v>70</v>
-      </c>
-      <c r="B31" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C31" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D31" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E31" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A32" s="13" t="s">
-        <v>71</v>
-      </c>
-      <c r="B32" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="C32" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D32" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E32" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="13" t="s">
-        <v>72</v>
-      </c>
-      <c r="B33" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="C33" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D33" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E33" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="13" t="s">
-        <v>73</v>
-      </c>
-      <c r="B34" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C34" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D34" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E34" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="13" t="s">
-        <v>74</v>
-      </c>
-      <c r="B35" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="C35" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D35" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E35" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="13" t="s">
-        <v>75</v>
-      </c>
-      <c r="B36" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="C36" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D36" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E36" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="13" t="s">
-        <v>95</v>
-      </c>
-      <c r="B37" s="13" t="s">
-        <v>96</v>
-      </c>
-      <c r="C37" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D37" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E37" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="13" t="s">
-        <v>77</v>
-      </c>
-      <c r="B38" s="13" t="s">
-        <v>97</v>
-      </c>
-      <c r="C38" s="6" t="b">
-        <v>1</v>
-      </c>
-      <c r="D38" s="6" t="b">
-        <v>0</v>
-      </c>
-      <c r="E38" s="6" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="13" t="s">
-        <v>76</v>
-      </c>
-      <c r="B39" s="13" t="s">
-        <v>98</v>
-      </c>
-      <c r="C39" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="D39" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E39" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="13" t="s">
-        <v>99</v>
-      </c>
-      <c r="B40" s="13" t="s">
-        <v>100</v>
-      </c>
-      <c r="C40" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="D40" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E40" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="13" t="s">
-        <v>78</v>
-      </c>
-      <c r="B41" s="13" t="s">
-        <v>101</v>
-      </c>
-      <c r="C41" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="D41" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E41" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A42" s="13" t="s">
-        <v>102</v>
-      </c>
-      <c r="B42" s="13" t="s">
-        <v>103</v>
-      </c>
-      <c r="C42" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="D42" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E42" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A43" s="13" t="s">
-        <v>104</v>
-      </c>
-      <c r="B43" s="13" t="s">
-        <v>105</v>
-      </c>
-      <c r="C43" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="D43" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E43" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A44" s="13" t="s">
-        <v>79</v>
-      </c>
-      <c r="B44" s="13" t="s">
-        <v>106</v>
-      </c>
-      <c r="C44" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="D44" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E44" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A45" s="13" t="s">
-        <v>80</v>
-      </c>
-      <c r="B45" s="13" t="s">
-        <v>107</v>
-      </c>
-      <c r="C45" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="D45" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E45" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A46" s="13" t="s">
-        <v>81</v>
-      </c>
-      <c r="B46" s="13" t="s">
-        <v>108</v>
-      </c>
-      <c r="C46" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="D46" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E46" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A47" s="12" t="s">
-        <v>82</v>
-      </c>
-      <c r="B47" s="12" t="s">
+      <c r="C47" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="D47" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E47" s="8" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A48" s="11" t="s">
         <v>28</v>
       </c>
-      <c r="C47" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="D47" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E47" s="8" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A48" s="12" t="s">
+      <c r="B48" s="11" t="s">
         <v>29</v>
       </c>
-      <c r="B48" s="12" t="s">
+      <c r="C48" s="8" t="b">
+        <v>1</v>
+      </c>
+      <c r="D48" s="8" t="b">
+        <v>0</v>
+      </c>
+      <c r="E48" s="8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A49" s="11" t="s">
         <v>30</v>
       </c>
-      <c r="C48" s="8" t="b">
-        <v>1</v>
-      </c>
-      <c r="D48" s="8" t="b">
-        <v>0</v>
-      </c>
-      <c r="E48" s="8" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A49" s="12" t="s">
+      <c r="B49" s="11" t="s">
         <v>31</v>
-      </c>
-      <c r="B49" s="12" t="s">
-        <v>32</v>
       </c>
       <c r="C49" s="8" t="b">
         <v>0</v>
@@ -1717,54 +1716,50 @@
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="B51" s="3"/>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="B52" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="B52" s="1" t="s">
-        <v>51</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="B53" s="1" t="s">
         <v>52</v>
-      </c>
-      <c r="B53" s="1" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B54" s="1" t="s">
         <v>54</v>
-      </c>
-      <c r="B54" s="1" t="s">
-        <v>55</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B55" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B55" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A59" s="9"/>
-      <c r="B59" s="9"/>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A60" s="10"/>
-      <c r="B60" s="11"/>
-    </row>
-    <row r="68" spans="3:3" x14ac:dyDescent="0.3">
-      <c r="C68" s="9"/>
+      <c r="A60" s="9"/>
+      <c r="B60" s="10"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <ignoredErrors>
+    <ignoredError sqref="A3:A52" evalError="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>